--- a/AI VS ME LOGS.xlsx
+++ b/AI VS ME LOGS.xlsx
@@ -1,48 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ab651a6d3c87b4/Documents/Desktop/AI_Assisted_Manual_testing/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_0E69F4ECD01BB1450A11F333262CA19D4AA775F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4184786D-E486-401D-ABAF-72D84B5F5118}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-93" yWindow="-93" windowWidth="21520" windowHeight="12800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="21520" windowHeight="12800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AI VS ME LOGS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+  <si>
+    <t>LOG_ID</t>
+  </si>
+  <si>
+    <t>FEATURE MODULE</t>
+  </si>
+  <si>
+    <t>WHAT AI GENERATED</t>
+  </si>
+  <si>
+    <t>WHAT I FOUND MANUALLY</t>
+  </si>
+  <si>
+    <t>DEFECT STATUS</t>
+  </si>
+  <si>
+    <t>LOG_001</t>
+  </si>
+  <si>
+    <t>FORGOT PASSWORD</t>
+  </si>
+  <si>
+    <t>TEST FORGOT PASSWORD OPTION ON LOGIN PAGE</t>
+  </si>
+  <si>
+    <t>NO FORGOT PASSWORD OPTION IS AVAILABLE ON THE LOGIN PAGE.</t>
+  </si>
+  <si>
+    <t>FAIL (MISSING FEATURE)</t>
+  </si>
+  <si>
+    <t>LOG_002</t>
+  </si>
+  <si>
+    <t>USER ID RULES</t>
+  </si>
+  <si>
+    <t>TEST VALID 10-DIGIT MOBILE NUMBER AS USER ID</t>
+  </si>
+  <si>
+    <t>SAUCEDEMO DOES NOT PROVIDE A 10-DIGIT MOBILE NUMBER USER ID RULE.</t>
+  </si>
+  <si>
+    <t>FAIL (RULE NOT IMPLEMENTED)</t>
+  </si>
+  <si>
+    <t>LOG_003</t>
+  </si>
+  <si>
+    <t>SEARCH BAR</t>
+  </si>
+  <si>
+    <t>TEST PRODUCT SEARCH BAR FUNCTIONALITY</t>
+  </si>
+  <si>
+    <t>NO SEARCH BAR IS AVAILABLE ON THE PRODUCTS PAGE.</t>
+  </si>
+  <si>
+    <t>LOG_004</t>
+  </si>
+  <si>
+    <t>PRODUCT FILTER</t>
+  </si>
+  <si>
+    <t>TEST PRODUCT CATEGORY FILTER COMPONENT</t>
+  </si>
+  <si>
+    <t>SAUCEDEMO DOES NOT HAVE A PRODUCT WISE FILTERING FEATURE.</t>
+  </si>
+  <si>
+    <t>LOG_005</t>
+  </si>
+  <si>
+    <t>CART QUANTITY</t>
+  </si>
+  <si>
+    <t>TEST QUANTITY CONTROLS IN CART VIEW</t>
+  </si>
+  <si>
+    <t>NO PLUS QUANTITY CONTROL IS AVAILABLE IN THE CART VIEW.</t>
+  </si>
+  <si>
+    <t>LOG_006</t>
+  </si>
+  <si>
+    <t>PAYMENT FIELDS</t>
+  </si>
+  <si>
+    <t>TEST PAYMENT CARD NUMBER FIELD IN CHECKOUT</t>
+  </si>
+  <si>
+    <t>SAUCEDEMO DOES NOT PROVIDE A PAYMENT CARD NUMBER SELECTION FIELD.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -61,90 +164,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -444,208 +488,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col width="13.9375" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18.29296875" customWidth="1" min="3" max="3"/>
-    <col width="26.05859375" customWidth="1" min="4" max="4"/>
-    <col width="17.05859375" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="5.76171875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.52734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.52734375" customWidth="1"/>
+    <col min="5" max="5" width="21.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LOG_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>FEATURE MODULE</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>WHAT AI GENERATED</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>WHAT I FOUND MANUALLY</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DEFECT STATUS</t>
-        </is>
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="62" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>LOG_001</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>FORGOT PASSWORD</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>TEST FORGOT PASSWORD OPTION ON LOGIN PAGE</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>NO FORGOT PASSWORD OPTION IS AVAILABLE ON THE LOGIN PAGE.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>FAIL (MISSING FEATURE)</t>
-        </is>
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" ht="62" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>LOG_002</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>USER ID RULES</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>TEST VALID 10-DIGIT MOBILE NUMBER AS USER ID</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SAUCEDEMO DOES NOT PROVIDE A 10-DIGIT MOBILE NUMBER USER ID RULE.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FAIL (RULE NOT IMPLEMENTED)</t>
-        </is>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" ht="62" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>LOG_003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>SEARCH BAR</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>TEST PRODUCT SEARCH BAR FUNCTIONALITY</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>NO SEARCH BAR IS AVAILABLE ON THE PRODUCTS PAGE.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FAIL (MISSING FEATURE)</t>
-        </is>
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="5" ht="72.34999999999999" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>LOG_004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>PRODUCT FILTER</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>TEST PRODUCT CATEGORY FILTER COMPONENT</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>SAUCEDEMO DOES NOT HAVE A PRODUCT WISE FILTERING FEATURE.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FAIL (MISSING FEATURE)</t>
-        </is>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="6" ht="62" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>LOG_005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CART QUANTITY</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>TEST QUANTITY CONTROLS IN CART VIEW</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>NO PLUS QUANTITY CONTROL IS AVAILABLE IN THE CART VIEW.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>FAIL (MISSING FEATURE)</t>
-        </is>
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" ht="82.7" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>LOG_006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>PAYMENT FIELDS</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>TEST PAYMENT CARD NUMBER FIELD IN CHECKOUT</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>SAUCEDEMO DOES NOT PROVIDE A PAYMENT CARD NUMBER SELECTION FIELD.</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FAIL (MISSING FEATURE)</t>
-        </is>
+    <row r="7" spans="1:5" s="2" customFormat="1" ht="10.35" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
